--- a/data/trans_dic/P25A$medico-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,96; 42,98</t>
+          <t>32,02; 42,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,13; 34,21</t>
+          <t>24,09; 33,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 31,24</t>
+          <t>20,13; 31,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 26,44</t>
+          <t>6,18; 26,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,58; 31,11</t>
+          <t>12,24; 31,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 21,55</t>
+          <t>2,48; 19,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,1; 39,47</t>
+          <t>29,56; 38,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,23; 32,31</t>
+          <t>23,47; 32,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,99; 27,96</t>
+          <t>17,78; 28,08</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 24,93</t>
+          <t>14,15; 24,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 16,41</t>
+          <t>9,12; 16,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 21,22</t>
+          <t>12,49; 21,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 13,18</t>
+          <t>4,03; 12,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 12,31</t>
+          <t>4,48; 12,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,97</t>
+          <t>7,3; 16,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 18,55</t>
+          <t>10,92; 18,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,35</t>
+          <t>7,87; 13,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 18,11</t>
+          <t>11,38; 17,83</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 21,95</t>
+          <t>6,64; 22,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 20,05</t>
+          <t>6,11; 20,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 22,69</t>
+          <t>6,49; 23,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>1,87; 15,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,98</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,57</t>
+          <t>1,98; 11,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 17,08</t>
+          <t>5,32; 16,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,82</t>
+          <t>3,64; 12,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 14,23</t>
+          <t>5,6; 14,77</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,46; 30,66</t>
+          <t>23,79; 30,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,57</t>
+          <t>16,95; 22,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,04; 22,65</t>
+          <t>16,28; 22,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,31</t>
+          <t>5,14; 12,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,19</t>
+          <t>6,25; 12,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,73</t>
+          <t>6,36; 12,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 24,54</t>
+          <t>19,02; 24,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,96; 18,48</t>
+          <t>14,13; 18,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 18,05</t>
+          <t>13,34; 17,98</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96862; 130251</t>
+          <t>97029; 128440</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89777; 127273</t>
+          <t>89625; 125805</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41811; 65548</t>
+          <t>42243; 66307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2937; 12734</t>
+          <t>2978; 12748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7999; 21488</t>
+          <t>8458; 22087</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>959; 8109</t>
+          <t>933; 7271</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>102204; 138627</t>
+          <t>103824; 136105</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>102491; 142544</t>
+          <t>103536; 142520</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44525; 69195</t>
+          <t>44000; 69486</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35106; 59108</t>
+          <t>33556; 57591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30491; 57055</t>
+          <t>31712; 56894</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37233; 64106</t>
+          <t>37724; 65749</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5543; 19932</t>
+          <t>6090; 19168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10465; 29566</t>
+          <t>10762; 28852</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13529; 32115</t>
+          <t>14678; 32842</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42972; 72022</t>
+          <t>42391; 71433</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46723; 78488</t>
+          <t>46291; 77219</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57604; 91110</t>
+          <t>57237; 89695</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5115; 18537</t>
+          <t>5606; 19006</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5573; 19299</t>
+          <t>5880; 19589</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5935; 20330</t>
+          <t>5816; 21152</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7873</t>
+          <t>960; 8052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6173</t>
+          <t>0; 6814</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1887; 10999</t>
+          <t>1886; 10580</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7703; 23194</t>
+          <t>7219; 22203</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6990; 22272</t>
+          <t>6326; 22481</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9930; 26274</t>
+          <t>10348; 27274</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>146547; 191499</t>
+          <t>148595; 191333</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>137926; 184183</t>
+          <t>138297; 185369</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96472; 136205</t>
+          <t>97948; 137652</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13395; 33379</t>
+          <t>12894; 30914</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24372; 47132</t>
+          <t>24164; 47385</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20931; 42491</t>
+          <t>21228; 43145</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>166235; 214789</t>
+          <t>166517; 214680</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>167872; 222191</t>
+          <t>169939; 222787</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122138; 168766</t>
+          <t>124792; 168185</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$medico-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,02; 42,38</t>
+          <t>31,73; 42,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,09; 33,81</t>
+          <t>24,08; 33,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 31,6</t>
+          <t>20,14; 31,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 26,47</t>
+          <t>6,33; 27,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 31,98</t>
+          <t>12,04; 31,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 19,32</t>
+          <t>2,57; 21,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,56; 38,75</t>
+          <t>29,59; 39,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,47; 32,31</t>
+          <t>23,23; 31,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,78; 28,08</t>
+          <t>17,63; 28,29</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 24,29</t>
+          <t>15,07; 24,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 16,36</t>
+          <t>9,14; 16,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 21,77</t>
+          <t>12,31; 21,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 12,68</t>
+          <t>3,61; 12,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 12,02</t>
+          <t>4,32; 11,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 16,33</t>
+          <t>6,88; 15,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 18,4</t>
+          <t>11,6; 18,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 13,14</t>
+          <t>8,06; 13,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 17,83</t>
+          <t>11,32; 17,4</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 22,51</t>
+          <t>6,06; 22,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 20,35</t>
+          <t>6,11; 20,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 23,6</t>
+          <t>7,01; 23,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 15,68</t>
+          <t>1,88; 14,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 9,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,13</t>
+          <t>1,96; 11,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 16,35</t>
+          <t>5,26; 15,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,95</t>
+          <t>4,07; 13,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 14,77</t>
+          <t>5,26; 14,58</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 30,63</t>
+          <t>23,81; 30,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,95; 22,71</t>
+          <t>16,94; 22,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,28; 22,89</t>
+          <t>15,74; 22,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,33</t>
+          <t>5,37; 12,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,26</t>
+          <t>6,2; 12,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,93</t>
+          <t>6,25; 12,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,02; 24,53</t>
+          <t>19,03; 24,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,13; 18,52</t>
+          <t>14,09; 18,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,34; 17,98</t>
+          <t>13,19; 18,05</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97029; 128440</t>
+          <t>96164; 129536</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89625; 125805</t>
+          <t>89579; 125280</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42243; 66307</t>
+          <t>42258; 66486</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2978; 12748</t>
+          <t>3050; 13214</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8458; 22087</t>
+          <t>8318; 21674</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>933; 7271</t>
+          <t>966; 8212</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>103824; 136105</t>
+          <t>103925; 138708</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>103536; 142520</t>
+          <t>102458; 140444</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44000; 69486</t>
+          <t>43625; 70007</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33556; 57591</t>
+          <t>35716; 59150</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31712; 56894</t>
+          <t>31796; 57416</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37724; 65749</t>
+          <t>37178; 64230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6090; 19168</t>
+          <t>5461; 19606</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10762; 28852</t>
+          <t>10362; 28759</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14678; 32842</t>
+          <t>13830; 31272</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42391; 71433</t>
+          <t>45038; 71736</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46291; 77219</t>
+          <t>47375; 77132</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57237; 89695</t>
+          <t>56964; 87559</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5606; 19006</t>
+          <t>5119; 18754</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5880; 19589</t>
+          <t>5884; 19610</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5816; 21152</t>
+          <t>6278; 21287</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>960; 8052</t>
+          <t>967; 7222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6814</t>
+          <t>0; 7255</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1886; 10580</t>
+          <t>1867; 11073</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7219; 22203</t>
+          <t>7147; 21312</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6326; 22481</t>
+          <t>7060; 23990</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10348; 27274</t>
+          <t>9717; 26918</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148595; 191333</t>
+          <t>148718; 190845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138297; 185369</t>
+          <t>138274; 185072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97948; 137652</t>
+          <t>94682; 134072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12894; 30914</t>
+          <t>13457; 31506</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24164; 47385</t>
+          <t>23978; 46866</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21228; 43145</t>
+          <t>20873; 42127</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>166517; 214680</t>
+          <t>166531; 214916</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>169939; 222787</t>
+          <t>169436; 221388</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124792; 168185</t>
+          <t>123358; 168823</t>
         </is>
       </c>
     </row>
